--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20889</v>
+        <v>26239</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26239</v>
+        <v>29622</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29622</v>
+        <v>31072</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31072</v>
+        <v>32159</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32159</v>
+        <v>35412</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35412</v>
+        <v>36059</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data/value_box.xlsx
+++ b/data/value_box.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36059</v>
+        <v>36103</v>
       </c>
     </row>
     <row r="3">
